--- a/Genshin_Crafting_TestCases.xlsx
+++ b/Genshin_Crafting_TestCases.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="81">
   <si>
     <t>用例编号</t>
   </si>
@@ -56,6 +56,9 @@
     <t>实际测试结果</t>
   </si>
   <si>
+    <t>录屏</t>
+  </si>
+  <si>
     <t>TC-001</t>
   </si>
   <si>
@@ -95,157 +98,181 @@
     <t>消耗3个2星材料；获得1个3星材料</t>
   </si>
   <si>
+    <t>TC-003</t>
+  </si>
+  <si>
+    <t>合成多个数量（5个）</t>
+  </si>
+  <si>
+    <t>玩家拥有至少15个1星材料，背包至少有5个空位</t>
+  </si>
+  <si>
+    <t>1.打开合成台；2.选择1星→2星配方；3.数量设为5；4.点击合成</t>
+  </si>
+  <si>
+    <t>消耗15个1星材料；获得5个2星材料</t>
+  </si>
+  <si>
     <t>TC-004</t>
   </si>
   <si>
-    <t>合成多个数量（5个）</t>
-  </si>
-  <si>
-    <t>玩家拥有至少15个1星材料，背包至少有5个空位</t>
-  </si>
-  <si>
-    <t>1.打开合成台；2.选择1星→2星配方；3.数量设为5；4.点击合成</t>
-  </si>
-  <si>
-    <t>消耗15个1星材料；获得5个2星材料</t>
+    <t>合成最大数量（999）</t>
+  </si>
+  <si>
+    <t>玩家拥有至少2997个1星材料，背包至少有999个空位</t>
+  </si>
+  <si>
+    <t>1.打开合成台；2.选择1星→2星配方；3.滑动或输入数量至999；4.点击合成</t>
+  </si>
+  <si>
+    <t>消耗2997个1星材料；获得999个2星材料；合成成功</t>
+  </si>
+  <si>
+    <t>中</t>
   </si>
   <si>
     <t>TC-005</t>
   </si>
   <si>
-    <t>合成最大数量（999）</t>
-  </si>
-  <si>
-    <t>玩家拥有至少2997个1星材料，背包至少有999个空位</t>
-  </si>
-  <si>
-    <t>1.打开合成台；2.选择1星→2星配方；3.滑动或输入数量至999；4.点击合成</t>
-  </si>
-  <si>
-    <t>消耗2997个1星材料；获得999个2星材料；合成成功</t>
-  </si>
-  <si>
-    <t>中</t>
+    <t>材料不足（差一个）</t>
+  </si>
+  <si>
+    <t>玩家拥有2个1星材料，背包有空位</t>
+  </si>
+  <si>
+    <t>1.打开合成台；2.选择1星→2星配方；3.尝试合成数量1</t>
+  </si>
+  <si>
+    <t>系统提示材料不足；无法合成；材料未消耗</t>
   </si>
   <si>
     <t>TC-006</t>
   </si>
   <si>
-    <t>材料不足（差一个）</t>
-  </si>
-  <si>
-    <t>玩家拥有2个1星材料，背包有空位</t>
-  </si>
-  <si>
-    <t>1.打开合成台；2.选择1星→2星配方；3.尝试合成数量1</t>
-  </si>
-  <si>
-    <t>系统提示材料不足；无法合成；材料未消耗</t>
+    <t>材料完全不足</t>
+  </si>
+  <si>
+    <t>玩家无1星材料</t>
+  </si>
+  <si>
+    <t>1.打开合成台；2.选择1星→2星配方；3.观察界面</t>
+  </si>
+  <si>
+    <t>合成按钮不可用；显示材料不足提示</t>
   </si>
   <si>
     <t>TC-007</t>
   </si>
   <si>
-    <t>材料完全不足</t>
-  </si>
-  <si>
-    <t>玩家无1星材料</t>
-  </si>
-  <si>
-    <t>1.打开合成台；2.选择1星→2星配方；3.观察界面</t>
-  </si>
-  <si>
-    <t>合成按钮不可用；显示材料不足提示</t>
+    <t>取消合成操作</t>
+  </si>
+  <si>
+    <t>玩家已打开合成界面并设定了数量但未点击合成</t>
+  </si>
+  <si>
+    <t>1.打开合成台；2.选择配方；3.设定数量；4.点击取消按钮或关闭界面</t>
+  </si>
+  <si>
+    <t>界面关闭；材料未消耗；背包不变</t>
+  </si>
+  <si>
+    <t>TC-008</t>
+  </si>
+  <si>
+    <t>合成后背包空间变化</t>
+  </si>
+  <si>
+    <t>玩家背包有3个1星材料（堆叠），无2星材料，有空位</t>
+  </si>
+  <si>
+    <t>1.打开合成台；2.选择配方；3.数量1；4.合成；5.检查背包</t>
+  </si>
+  <si>
+    <t>1星材料数量减少3；2星材料数量增加1；背包总格子数可能不变（堆叠）</t>
+  </si>
+  <si>
+    <t>TC-009</t>
+  </si>
+  <si>
+    <t>背包满时合成（空间不足）</t>
+  </si>
+  <si>
+    <t>玩家背包所有格子已满（材料所在堆叠&gt;1，不会释放空格），且背包中无合成产品</t>
+  </si>
+  <si>
+    <t>1.打开合成台；2.选择配方；3.尝试合成1个</t>
+  </si>
+  <si>
+    <t>系统提示“背包空间不足”；合成失败；材料不消耗</t>
   </si>
   <si>
     <t>TC-010</t>
   </si>
   <si>
-    <t>取消合成操作</t>
-  </si>
-  <si>
-    <t>玩家已打开合成界面并设定了数量但未点击合成</t>
-  </si>
-  <si>
-    <t>1.打开合成台；2.选择配方；3.设定数量；4.点击取消按钮或关闭界面</t>
-  </si>
-  <si>
-    <t>界面关闭；材料未消耗；背包不变</t>
+    <t>不同城市合成台功能一致</t>
+  </si>
+  <si>
+    <t>玩家在蒙德和璃月均有合成台，材料足够各合成一次</t>
+  </si>
+  <si>
+    <t>1.在蒙德合成台选择1星→2星配方合成1个；2.在璃月合成台同样操作</t>
+  </si>
+  <si>
+    <t>两次合成消耗和产出一致；功能无差异</t>
   </si>
   <si>
     <t>TC-011</t>
   </si>
   <si>
-    <t>合成后背包空间变化</t>
-  </si>
-  <si>
-    <t>玩家背包有3个1星材料（堆叠），无2星材料，有空位</t>
-  </si>
-  <si>
-    <t>1.打开合成台；2.选择配方；3.数量1；4.合成；5.检查背包</t>
-  </si>
-  <si>
-    <t>1星材料数量减少3；2星材料数量增加1；背包总格子数可能不变（堆叠）</t>
+    <t>不同配方合成（不同种类）</t>
+  </si>
+  <si>
+    <t>玩家拥有破损的面具和混沌装置各3个（均为1星）</t>
+  </si>
+  <si>
+    <t>1.分别选择破损的面具→沉重面具配方合成1个；2.选择混沌装置→混沌回路配方合成1个</t>
+  </si>
+  <si>
+    <t>每个配方消耗对应的3个1星材料；产出对应的2星材料</t>
   </si>
   <si>
     <t>TC-012</t>
   </si>
   <si>
-    <t>背包满时合成（空间不足）</t>
-  </si>
-  <si>
-    <t>玩家背包所有格子已满（材料所在堆叠&gt;1，不会释放空格），且背包中无合成产品</t>
-  </si>
-  <si>
-    <t>1.打开合成台；2.选择配方；3.尝试合成1个</t>
-  </si>
-  <si>
-    <t>系统提示“背包空间不足”；合成失败；材料不消耗</t>
+    <t>连续多次合成（手动）</t>
+  </si>
+  <si>
+    <t>玩家拥有9个1星材料</t>
+  </si>
+  <si>
+    <t>1.合成1个（消耗3）；2.再次打开合成台；3.再合成1个（消耗3）；4.再合成1个</t>
+  </si>
+  <si>
+    <t>每次合成成功；三次后材料从9减为0；产品增加3个</t>
   </si>
   <si>
     <t>TC-013</t>
   </si>
   <si>
-    <t>不同城市合成台功能一致</t>
-  </si>
-  <si>
-    <t>玩家在蒙德和璃月均有合成台，材料足够各合成一次</t>
-  </si>
-  <si>
-    <t>1.在蒙德合成台选择1星→2星配方合成1个；2.在璃月合成台同样操作</t>
-  </si>
-  <si>
-    <t>两次合成消耗和产出一致；功能无差异</t>
-  </si>
-  <si>
-    <t>TC-014</t>
-  </si>
-  <si>
-    <t>不同配方合成（不同种类）</t>
-  </si>
-  <si>
-    <t>玩家拥有破损的面具和混沌装置各3个（均为1星）</t>
-  </si>
-  <si>
-    <t>1.分别选择破损的面具→沉重面具配方合成1个；2.选择混沌装置→混沌回路配方合成1个</t>
-  </si>
-  <si>
-    <t>每个配方消耗对应的3个1星材料；产出对应的2星材料</t>
-  </si>
-  <si>
-    <t>TC-015</t>
-  </si>
-  <si>
-    <t>连续多次合成（手动）</t>
-  </si>
-  <si>
-    <t>玩家拥有9个1星材料</t>
-  </si>
-  <si>
-    <t>1.合成1个（消耗3）；2.再次打开合成台；3.再合成1个（消耗3）；4.再合成1个</t>
-  </si>
-  <si>
-    <t>每次合成成功；三次后材料从9减为0；产品增加3个</t>
+    <t>角色界面</t>
+  </si>
+  <si>
+    <t>点击纪行界面的“任务”按钮动画效果</t>
+  </si>
+  <si>
+    <t>打开至“纪行”界面</t>
+  </si>
+  <si>
+    <t>1.点击“任务”按钮 2.观察按钮动画效果</t>
+  </si>
+  <si>
+    <t>点击按钮时按键应由白变黑并出现白色圆框背景</t>
+  </si>
+  <si>
+    <t>点击瞬间“任务”按键闪烁抽动</t>
+  </si>
+  <si>
+    <t>click_bug.mp4</t>
   </si>
 </sst>
 </file>
@@ -1400,20 +1427,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="7"/>
+  <dimension ref="A1:I14"/>
+  <sheetFormatPr defaultColWidth="76.6363636363636" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9.54545454545454" customWidth="1"/>
     <col min="2" max="2" width="11.8181818181818" customWidth="1"/>
-    <col min="3" max="3" width="30.9090909090909" customWidth="1"/>
-    <col min="4" max="4" width="84.9090909090909" customWidth="1"/>
-    <col min="5" max="5" width="88.2727272727273" customWidth="1"/>
-    <col min="6" max="6" width="72.5454545454545" customWidth="1"/>
+    <col min="3" max="3" width="38.8181818181818" customWidth="1"/>
+    <col min="4" max="4" width="76.9090909090909" customWidth="1"/>
+    <col min="5" max="5" width="79.9090909090909" customWidth="1"/>
+    <col min="6" max="6" width="64.6363636363636" customWidth="1"/>
     <col min="7" max="7" width="7.54545454545455" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="8" max="8" width="32" customWidth="1"/>
+    <col min="9" max="9" width="15.1818181818182" customWidth="1"/>
+    <col min="10" max="16384" width="76.6363636363636" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:8">
+    <row r="1" s="1" customFormat="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1438,317 +1467,349 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" t="s">
         <v>15</v>
       </c>
+      <c r="H3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="3" spans="1:8">
-      <c r="A3" t="s">
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" t="s">
         <v>16</v>
       </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" t="s">
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" t="s">
         <v>15</v>
       </c>
+      <c r="H6" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="4" spans="1:8">
-      <c r="A4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" t="s">
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" t="s">
         <v>15</v>
       </c>
+      <c r="H7" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="5" spans="1:8">
-      <c r="A5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H5" t="s">
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" t="s">
+        <v>50</v>
+      </c>
+      <c r="E9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" t="s">
+        <v>52</v>
+      </c>
+      <c r="G9" t="s">
+        <v>32</v>
+      </c>
+      <c r="H9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" t="s">
+        <v>57</v>
+      </c>
+      <c r="G10" t="s">
         <v>15</v>
       </c>
+      <c r="H10" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="6" spans="1:8">
-      <c r="A6" t="s">
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" t="s">
+        <v>60</v>
+      </c>
+      <c r="E11" t="s">
+        <v>61</v>
+      </c>
+      <c r="F11" t="s">
+        <v>62</v>
+      </c>
+      <c r="G11" t="s">
         <v>32</v>
       </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" t="s">
-        <v>35</v>
-      </c>
-      <c r="F6" t="s">
-        <v>36</v>
-      </c>
-      <c r="G6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" t="s">
-        <v>15</v>
+      <c r="H11" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
-      <c r="A7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" t="s">
-        <v>41</v>
-      </c>
-      <c r="G7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" t="s">
-        <v>15</v>
+    <row r="12" spans="1:9">
+      <c r="A12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12" t="s">
+        <v>65</v>
+      </c>
+      <c r="E12" t="s">
+        <v>66</v>
+      </c>
+      <c r="F12" t="s">
+        <v>67</v>
+      </c>
+      <c r="G12" t="s">
+        <v>32</v>
+      </c>
+      <c r="H12" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
-      <c r="A8" t="s">
-        <v>42</v>
-      </c>
-      <c r="B8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E8" t="s">
-        <v>45</v>
-      </c>
-      <c r="F8" t="s">
-        <v>46</v>
-      </c>
-      <c r="G8" t="s">
-        <v>31</v>
-      </c>
-      <c r="H8" t="s">
-        <v>15</v>
+    <row r="13" spans="1:9">
+      <c r="A13" t="s">
+        <v>68</v>
+      </c>
+      <c r="B13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D13" t="s">
+        <v>70</v>
+      </c>
+      <c r="E13" t="s">
+        <v>71</v>
+      </c>
+      <c r="F13" t="s">
+        <v>72</v>
+      </c>
+      <c r="G13" t="s">
+        <v>32</v>
+      </c>
+      <c r="H13" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
-      <c r="A9" t="s">
-        <v>47</v>
-      </c>
-      <c r="B9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" t="s">
-        <v>48</v>
-      </c>
-      <c r="D9" t="s">
-        <v>49</v>
-      </c>
-      <c r="E9" t="s">
-        <v>50</v>
-      </c>
-      <c r="F9" t="s">
-        <v>51</v>
-      </c>
-      <c r="G9" t="s">
-        <v>31</v>
-      </c>
-      <c r="H9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" t="s">
-        <v>52</v>
-      </c>
-      <c r="B10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" t="s">
-        <v>53</v>
-      </c>
-      <c r="D10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E10" t="s">
-        <v>55</v>
-      </c>
-      <c r="F10" t="s">
-        <v>56</v>
-      </c>
-      <c r="G10" t="s">
-        <v>14</v>
-      </c>
-      <c r="H10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" t="s">
-        <v>57</v>
-      </c>
-      <c r="B11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" t="s">
-        <v>58</v>
-      </c>
-      <c r="D11" t="s">
-        <v>59</v>
-      </c>
-      <c r="E11" t="s">
-        <v>60</v>
-      </c>
-      <c r="F11" t="s">
-        <v>61</v>
-      </c>
-      <c r="G11" t="s">
-        <v>31</v>
-      </c>
-      <c r="H11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" t="s">
-        <v>62</v>
-      </c>
-      <c r="B12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" t="s">
-        <v>63</v>
-      </c>
-      <c r="D12" t="s">
-        <v>64</v>
-      </c>
-      <c r="E12" t="s">
-        <v>65</v>
-      </c>
-      <c r="F12" t="s">
-        <v>66</v>
-      </c>
-      <c r="G12" t="s">
-        <v>31</v>
-      </c>
-      <c r="H12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" t="s">
-        <v>67</v>
-      </c>
-      <c r="B13" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" t="s">
-        <v>68</v>
-      </c>
-      <c r="D13" t="s">
-        <v>69</v>
-      </c>
-      <c r="E13" t="s">
-        <v>70</v>
-      </c>
-      <c r="F13" t="s">
-        <v>71</v>
-      </c>
-      <c r="G13" t="s">
-        <v>31</v>
-      </c>
-      <c r="H13" t="s">
-        <v>15</v>
+    <row r="14" spans="1:9">
+      <c r="A14" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C14" t="s">
+        <v>75</v>
+      </c>
+      <c r="D14" t="s">
+        <v>76</v>
+      </c>
+      <c r="E14" t="s">
+        <v>77</v>
+      </c>
+      <c r="F14" t="s">
+        <v>78</v>
+      </c>
+      <c r="G14" t="s">
+        <v>32</v>
+      </c>
+      <c r="H14" t="s">
+        <v>79</v>
+      </c>
+      <c r="I14" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
